--- a/FL-corrections-structure/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
+++ b/FL-corrections-structure/ig/CodeSystem-fr-core-cs-uf-indicateur.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-08T19:18:35+00:00</t>
+    <t>2026-03-11T17:39:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
